--- a/复采名单.xlsx
+++ b/复采名单.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MAC热吻棒67</t>
+          <t>NARS 超方瓶粉底液#L1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NARS超方瓶粉底液L4</t>
+          <t>拉夫劳伦俱乐部香水淡香型 100ML</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -530,12 +530,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>澳洲木瓜膏16g</t>
+          <t>NARS液体腮红 INSATIABLE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -546,490 +546,6 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TF白麝香 100ml</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>77</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>黛珂AQ舒活白檀美白乳液200ml</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>80</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>黛珂牛油果乳液 300ml</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>83</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>黛珂散粉01 24年新版</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>85</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>黛珂紫苏水 300ml</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>88</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>费列罗榛果巧克力制品T24</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>144</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>蔻依北国雪松浓香水50ml</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>152</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>拉夫劳伦地球系列香氛 澳洲檀木 100ml</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>175</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>罗拉散粉经典款29G</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>177</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>慕拉得塑颜修复A醇精华30ml</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>191</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>269</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>圣罗兰黑色皮革气垫B10</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>293</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">阿玛尼权力PR0粉底1.5 30ml </t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>304</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>GUCCI花悦绽放100ML浓香</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>310</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>赫莲娜绿宝瓶新肌水400ml</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>311</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>赫莲娜绿宝瓶新肌水200ml</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>354</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>娇韵诗双萃焕活修护精华露100ml</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>358</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>YSL圣罗兰黑金方管1968</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>374</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>爱马仕绯红火参古龙水100ml</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>398</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>马丁马吉拉-爵士酒廊淡香100ml</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>408</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>NARS液体腮红 INSATIABLE</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>421</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>伊丽莎白雅顿经典唇膏13g</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/复采名单.xlsx
+++ b/复采名单.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,11 +482,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NARS 超方瓶粉底液#L1</t>
+          <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,11 +504,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>拉夫劳伦俱乐部香水淡香型 100ML</t>
+          <t>NARS空气唇釉686 lose control</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -526,16 +526,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NARS液体腮红 INSATIABLE</t>
+          <t>SK-II光蕴臻采焕亮精华露双瓶装</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>已采集</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -546,6 +546,468 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰皮气垫新明彩亮润轻垫粉底液 #B20</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰皮气垫新明彩亮润轻垫粉底液 #B20</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>黛珂 防晒防水版60g</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>74</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>黛珂 植物韵律清爽水200ml</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>88</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>费列罗榛果巧克力制品T24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>146</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>拉夫劳伦地球淡香氛 40ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>147</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>拉夫劳伦地球系列淡香氛 安的列斯香根草 100ml</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>159</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">兰蔻 极光乳液净澈焕肤亮白乳液 75ml </t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>170</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>兰蔻是我淡香水 50ml</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>190</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>伟博金萃高纯度鱼油1100</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>191</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>332</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>338</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>馥蕾诗红茶精粹水250ml</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>347</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>科颜氏果冻清爽高保湿霜50ml/瓶</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>356</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管13色</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>373</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>爱马仕李先生的花园淡香水100ml</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>388</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N1 30ML 新版 2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>397</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园沐光橙香水100ML</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>410</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NARS THE MULTIPLE HOT TAKE 8G</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>438</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MAC魅可 聚光瓶粉底液 NW11 30ml</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>440</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MAC魅可 聚光瓶粉底液 NC12 30ml</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>已采集</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/复采名单.xlsx
+++ b/复采名单.xlsx
@@ -482,11 +482,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
+          <t>芭比波朗月光石眼影</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -557,7 +557,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -579,7 +579,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -601,7 +601,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -623,7 +623,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -689,7 +689,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -733,7 +733,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -799,7 +799,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -887,7 +887,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -909,7 +909,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -931,7 +931,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
